--- a/reports/2026-02-24.xlsx
+++ b/reports/2026-02-24.xlsx
@@ -554,7 +554,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-02-24 05:35 UTC</t>
+          <t>2026-02-24 12:35 UTC</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>52.33</v>
+        <v>60.68</v>
       </c>
       <c r="F2" t="n">
-        <v>52.33</v>
+        <v>60.68</v>
       </c>
       <c r="G2" t="n">
         <v>2</v>
@@ -735,7 +735,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>$3.96M</t>
+          <t>$3.80M</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -756,34 +756,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>pullback</t>
+          <t>reversal</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>45.6</v>
+        <v>52.98</v>
       </c>
       <c r="F3" t="n">
-        <v>45.6</v>
+        <v>52.98</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>$0.74</t>
+          <t>$0.73</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>$739.96M</t>
+          <t>$735.46M</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>$3.87M</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+          <t>$9.15M</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>overextended</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -791,12 +795,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BCHUSDT</t>
+          <t>XMRUSDT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bitcoin Cash</t>
+          <t>Monero</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -805,27 +809,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>44.91</v>
+        <v>41.16</v>
       </c>
       <c r="F4" t="n">
-        <v>44.91</v>
+        <v>41.16</v>
       </c>
       <c r="G4" t="n">
         <v>2</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>$486.90</t>
+          <t>$324.35</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>$9.75B</t>
+          <t>$5.98B</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>$21.02M</t>
+          <t>$3.28M</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -836,12 +840,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PUMPUSDT</t>
+          <t>POLUSDT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Pump.fun</t>
+          <t>Polygon (prev. MATIC)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -850,27 +854,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>44.82</v>
+        <v>40.48</v>
       </c>
       <c r="F5" t="n">
-        <v>44.82</v>
+        <v>40.48</v>
       </c>
       <c r="G5" t="n">
         <v>2</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>$0.00</t>
+          <t>$0.11</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>$614.35M</t>
+          <t>$1.12B</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>$2.26M</t>
+          <t>$1.42M</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -881,12 +885,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SEIUSDT</t>
+          <t>BCHUSDT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sei</t>
+          <t>Bitcoin Cash</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -895,27 +899,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>41.55</v>
+        <v>38.61</v>
       </c>
       <c r="F6" t="n">
-        <v>41.55</v>
+        <v>38.61</v>
       </c>
       <c r="G6" t="n">
         <v>2</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>$0.07</t>
+          <t>$476.90</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>$440.58M</t>
+          <t>$9.54B</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>$1.99M</t>
+          <t>$21.67M</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -926,12 +930,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>POLUSDT</t>
+          <t>LINKUSDT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Polygon (prev. MATIC)</t>
+          <t>Chainlink</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -940,27 +944,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>40.48</v>
+        <v>38.11</v>
       </c>
       <c r="F7" t="n">
-        <v>40.48</v>
+        <v>38.11</v>
       </c>
       <c r="G7" t="n">
         <v>2</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>$0.10</t>
+          <t>$8.18</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>$1.11B</t>
+          <t>$5.79B</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>$1.66M</t>
+          <t>$5.79M</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -995,17 +999,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>$3.22</t>
+          <t>$3.18</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>$321.91M</t>
+          <t>$317.95M</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>$1.46M</t>
+          <t>$1.66M</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1016,12 +1020,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HBARUSDT</t>
+          <t>WLFIUSDT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Hedera</t>
+          <t>World Liberty Financial</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1030,27 +1034,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>32.99</v>
+        <v>31.26</v>
       </c>
       <c r="F9" t="n">
-        <v>32.99</v>
+        <v>31.26</v>
       </c>
       <c r="G9" t="n">
         <v>2</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>$0.09</t>
+          <t>$0.11</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>$4.01B</t>
+          <t>$3.00B</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>$4.51M</t>
+          <t>$13.50M</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1061,12 +1065,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>UNIUSDT</t>
+          <t>MYXUSDT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Uniswap</t>
+          <t>MYX Finance</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1075,27 +1079,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>32.92</v>
+        <v>30</v>
       </c>
       <c r="F10" t="n">
-        <v>32.92</v>
+        <v>30</v>
       </c>
       <c r="G10" t="n">
         <v>2</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>$3.31</t>
+          <t>$0.47</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>$2.09B</t>
+          <t>$119.75M</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>$6.92M</t>
+          <t>$2.52M</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1106,12 +1110,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>WLFIUSDT</t>
+          <t>BDXUSDT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>World Liberty Financial</t>
+          <t>Beldex</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1120,27 +1124,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>31.26</v>
+        <v>29.78</v>
       </c>
       <c r="F11" t="n">
-        <v>31.26</v>
+        <v>29.78</v>
       </c>
       <c r="G11" t="n">
         <v>2</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>$0.11</t>
+          <t>$0.08</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>$2.95B</t>
+          <t>$609.85M</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>$14.22M</t>
+          <t>$1.31M</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1151,12 +1155,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MYXUSDT</t>
+          <t>DOTUSDT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MYX Finance</t>
+          <t>Polkadot</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1165,27 +1169,27 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>30</v>
+        <v>29.45</v>
       </c>
       <c r="F12" t="n">
-        <v>30</v>
+        <v>29.45</v>
       </c>
       <c r="G12" t="n">
         <v>2</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>$0.56</t>
+          <t>$1.24</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>$139.27M</t>
+          <t>$2.07B</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>$4.18M</t>
+          <t>$4.68M</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1196,12 +1200,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BDXUSDT</t>
+          <t>UNIUSDT</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Beldex</t>
+          <t>Uniswap</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1210,27 +1214,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>29.78</v>
+        <v>27.49</v>
       </c>
       <c r="F13" t="n">
-        <v>29.78</v>
+        <v>27.49</v>
       </c>
       <c r="G13" t="n">
         <v>2</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>$0.08</t>
+          <t>$3.33</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>$610.93M</t>
+          <t>$2.11B</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>$1.34M</t>
+          <t>$5.37M</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1241,12 +1245,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>WIFUSDT</t>
+          <t>TRUMPUSDT</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>dogwifhat</t>
+          <t>OFFICIAL TRUMP</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1255,27 +1259,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>28.73</v>
+        <v>27.47</v>
       </c>
       <c r="F14" t="n">
-        <v>28.73</v>
+        <v>27.47</v>
       </c>
       <c r="G14" t="n">
         <v>2</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>$0.20</t>
+          <t>$3.28</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>$197.47M</t>
+          <t>$762.64M</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>$1.11M</t>
+          <t>$3.62M</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1286,12 +1290,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ETHFIUSDT</t>
+          <t>LTCUSDT</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ether.fi</t>
+          <t>Litecoin</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1300,27 +1304,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>28.41</v>
+        <v>27.28</v>
       </c>
       <c r="F15" t="n">
-        <v>28.41</v>
+        <v>27.28</v>
       </c>
       <c r="G15" t="n">
         <v>2</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>$0.44</t>
+          <t>$50.82</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>$327.09M</t>
+          <t>$3.91B</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>$3.93M</t>
+          <t>$10.50M</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1331,12 +1335,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AVAXUSDT</t>
+          <t>ETCUSDT</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avalanche</t>
+          <t>Ethereum Classic</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1345,27 +1349,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>27.78</v>
+        <v>27.21</v>
       </c>
       <c r="F16" t="n">
-        <v>27.78</v>
+        <v>27.21</v>
       </c>
       <c r="G16" t="n">
         <v>2</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>$8.23</t>
+          <t>$8.18</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>$3.55B</t>
+          <t>$1.27B</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>$10.08M</t>
+          <t>$2.31M</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1376,12 +1380,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>TRUMPUSDT</t>
+          <t>HBARUSDT</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>OFFICIAL TRUMP</t>
+          <t>Hedera</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1390,27 +1394,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>27.47</v>
+        <v>27.17</v>
       </c>
       <c r="F17" t="n">
-        <v>27.47</v>
+        <v>27.17</v>
       </c>
       <c r="G17" t="n">
         <v>2</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>$3.24</t>
+          <t>$0.09</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>$753.45M</t>
+          <t>$4.03B</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>$3.41M</t>
+          <t>$4.09M</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1421,12 +1425,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LTCUSDT</t>
+          <t>NEARUSDT</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Litecoin</t>
+          <t>NEAR Protocol</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1435,27 +1439,27 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>27.42</v>
+        <v>26.84</v>
       </c>
       <c r="F18" t="n">
-        <v>27.42</v>
+        <v>26.84</v>
       </c>
       <c r="G18" t="n">
         <v>2</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>$50.47</t>
+          <t>$0.97</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>$3.88B</t>
+          <t>$1.25B</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>$9.56M</t>
+          <t>$3.41M</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1466,12 +1470,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ETCUSDT</t>
+          <t>CAKEUSDT</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ethereum Classic</t>
+          <t>PancakeSwap</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1480,27 +1484,27 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>27.21</v>
+        <v>26.77</v>
       </c>
       <c r="F19" t="n">
-        <v>27.21</v>
+        <v>26.77</v>
       </c>
       <c r="G19" t="n">
         <v>2</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>$8.17</t>
+          <t>$1.19</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>$1.27B</t>
+          <t>$394.65M</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>$2.81M</t>
+          <t>$1.68M</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1511,12 +1515,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LINKUSDT</t>
+          <t>FILUSDT</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chainlink</t>
+          <t>Filecoin</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1525,27 +1529,27 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>27.03</v>
+        <v>26.7</v>
       </c>
       <c r="F20" t="n">
-        <v>27.03</v>
+        <v>26.7</v>
       </c>
       <c r="G20" t="n">
         <v>2</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>$8.16</t>
+          <t>$0.88</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>$5.77B</t>
+          <t>$660.43M</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>$4.60M</t>
+          <t>$1.46M</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1556,12 +1560,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NEARUSDT</t>
+          <t>ATOMUSDT</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>NEAR Protocol</t>
+          <t>Cosmos</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1570,27 +1574,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>26.84</v>
+        <v>26.59</v>
       </c>
       <c r="F21" t="n">
-        <v>26.84</v>
+        <v>26.59</v>
       </c>
       <c r="G21" t="n">
         <v>2</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>$0.97</t>
+          <t>$2.04</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>$1.25B</t>
+          <t>$1.01B</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>$3.82M</t>
+          <t>$1.32M</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1712,11 +1716,11 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>$3.96M</t>
+          <t>$3.80M</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>52.33</v>
+        <v>60.68</v>
       </c>
       <c r="H2" t="n">
         <v>95.59999999999999</v>
@@ -1728,7 +1732,7 @@
         <v>60</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>27.83</v>
       </c>
       <c r="L2" t="inlineStr"/>
     </row>
@@ -1738,45 +1742,49 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BCHUSDT</t>
+          <t>PIPPINUSDT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bitcoin Cash</t>
+          <t>pippin</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>$486.90</t>
+          <t>$0.73</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>$9.75B</t>
+          <t>$735.46M</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>$21.02M</t>
+          <t>$9.15M</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>44.91</v>
+        <v>52.98</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>84.84999999999999</v>
+        <v>45.64</v>
       </c>
       <c r="J3" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="K3" t="n">
-        <v>38.19</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>overextended</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1784,43 +1792,43 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PUMPUSDT</t>
+          <t>XMRUSDT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Pump.fun</t>
+          <t>Monero</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>$0.00</t>
+          <t>$324.35</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>$614.35M</t>
+          <t>$5.98B</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>$2.26M</t>
+          <t>$3.28M</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>44.82</v>
+        <v>41.16</v>
       </c>
       <c r="H4" t="n">
         <v>100</v>
       </c>
       <c r="I4" t="n">
-        <v>70.23</v>
+        <v>83.62</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>79.17</v>
+        <v>53.59</v>
       </c>
       <c r="L4" t="inlineStr"/>
     </row>
@@ -1830,43 +1838,43 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SEIUSDT</t>
+          <t>POLUSDT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sei</t>
+          <t>Polygon (prev. MATIC)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>$0.07</t>
+          <t>$0.11</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>$440.58M</t>
+          <t>$1.12B</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>$1.99M</t>
+          <t>$1.42M</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>41.55</v>
+        <v>40.48</v>
       </c>
       <c r="H5" t="n">
-        <v>100</v>
+        <v>82.92</v>
       </c>
       <c r="I5" t="n">
-        <v>82.66</v>
+        <v>94.92</v>
       </c>
       <c r="J5" t="n">
+        <v>30</v>
+      </c>
+      <c r="K5" t="n">
         <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>55.86</v>
       </c>
       <c r="L5" t="inlineStr"/>
     </row>
@@ -1876,43 +1884,43 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>POLUSDT</t>
+          <t>BCHUSDT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Polygon (prev. MATIC)</t>
+          <t>Bitcoin Cash</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>$0.10</t>
+          <t>$476.90</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>$1.11B</t>
+          <t>$9.54B</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>$1.66M</t>
+          <t>$21.67M</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>40.48</v>
+        <v>38.61</v>
       </c>
       <c r="H6" t="n">
-        <v>82.92</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>94.92</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>17.18</v>
       </c>
       <c r="L6" t="inlineStr"/>
     </row>
@@ -1922,43 +1930,43 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>INJUSDT</t>
+          <t>LINKUSDT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Injective</t>
+          <t>Chainlink</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>$3.22</t>
+          <t>$8.18</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>$321.91M</t>
+          <t>$5.79B</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>$1.46M</t>
+          <t>$5.79M</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>33.91</v>
+        <v>38.11</v>
       </c>
       <c r="H7" t="n">
         <v>100</v>
       </c>
       <c r="I7" t="n">
-        <v>73.39</v>
+        <v>90.08</v>
       </c>
       <c r="J7" t="n">
-        <v>29.73</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>36.94</v>
       </c>
       <c r="L7" t="inlineStr"/>
     </row>
@@ -1968,43 +1976,43 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HBARUSDT</t>
+          <t>INJUSDT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Hedera</t>
+          <t>Injective</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>$0.09</t>
+          <t>$3.18</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>$4.01B</t>
+          <t>$317.95M</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>$4.51M</t>
+          <t>$1.66M</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>32.99</v>
+        <v>33.91</v>
       </c>
       <c r="H8" t="n">
         <v>100</v>
       </c>
       <c r="I8" t="n">
-        <v>90.56999999999999</v>
+        <v>73.39</v>
       </c>
       <c r="J8" t="n">
+        <v>29.73</v>
+      </c>
+      <c r="K8" t="n">
         <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>19.4</v>
       </c>
       <c r="L8" t="inlineStr"/>
     </row>
@@ -2014,43 +2022,43 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>UNIUSDT</t>
+          <t>WLFIUSDT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Uniswap</t>
+          <t>World Liberty Financial</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>$3.31</t>
+          <t>$0.11</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>$2.09B</t>
+          <t>$3.00B</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>$6.92M</t>
+          <t>$13.50M</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>32.92</v>
+        <v>31.26</v>
       </c>
       <c r="H9" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>91.63</v>
+        <v>79.84</v>
       </c>
       <c r="J9" t="n">
+        <v>18.27</v>
+      </c>
+      <c r="K9" t="n">
         <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>18.1</v>
       </c>
       <c r="L9" t="inlineStr"/>
     </row>
@@ -2060,49 +2068,45 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PIPPINUSDT</t>
+          <t>MYXUSDT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>pippin</t>
+          <t>MYX Finance</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>$0.74</t>
+          <t>$0.47</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>$739.96M</t>
+          <t>$119.75M</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>$3.87M</t>
+          <t>$2.52M</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>31.98</v>
+        <v>30</v>
       </c>
       <c r="H10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I10" t="n">
         <v>0</v>
       </c>
-      <c r="I10" t="n">
-        <v>45.64</v>
-      </c>
       <c r="J10" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>overextended</t>
-        </is>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -2110,40 +2114,40 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>WLFIUSDT</t>
+          <t>BDXUSDT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>World Liberty Financial</t>
+          <t>Beldex</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>$0.11</t>
+          <t>$0.08</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>$2.95B</t>
+          <t>$609.85M</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>$14.22M</t>
+          <t>$1.31M</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>31.26</v>
+        <v>29.78</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>79.84</v>
+        <v>99.28</v>
       </c>
       <c r="J11" t="n">
-        <v>18.27</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -2530,21 +2534,21 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>$0.74</t>
+          <t>$0.73</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>$739.96M</t>
+          <t>$735.46M</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>$3.87M</t>
+          <t>$9.15M</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>45.6</v>
+        <v>44</v>
       </c>
       <c r="H2" t="n">
         <v>60</v>
@@ -2553,10 +2557,10 @@
         <v>20</v>
       </c>
       <c r="J2" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L2" t="inlineStr"/>
     </row>
@@ -2586,11 +2590,11 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>$3.96M</t>
+          <t>$3.80M</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>41.6</v>
+        <v>40</v>
       </c>
       <c r="H3" t="n">
         <v>20</v>
@@ -2599,10 +2603,10 @@
         <v>80</v>
       </c>
       <c r="J3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>61.75</v>
       </c>
       <c r="L3" t="inlineStr"/>
     </row>
@@ -2627,12 +2631,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>$164.36M</t>
+          <t>$164.57M</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>$3.99M</t>
+          <t>$3.48M</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -2672,17 +2676,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>$0.10</t>
+          <t>$0.11</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>$1.11B</t>
+          <t>$1.12B</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>$1.66M</t>
+          <t>$1.42M</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -2727,16 +2731,16 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>$610.93M</t>
+          <t>$609.85M</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>$1.34M</t>
+          <t>$1.31M</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>20.8</v>
+        <v>20</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -2745,10 +2749,10 @@
         <v>100</v>
       </c>
       <c r="J6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -2772,17 +2776,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>$2.08</t>
+          <t>$2.04</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>$1.03B</t>
+          <t>$1.01B</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>$1.37M</t>
+          <t>$1.32M</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2812,31 +2816,31 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>WLFIUSDT</t>
+          <t>XMRUSDT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>World Liberty Financial</t>
+          <t>Monero</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>$0.11</t>
+          <t>$324.35</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>$2.95B</t>
+          <t>$5.98B</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>$14.22M</t>
+          <t>$3.28M</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>3.83</v>
+        <v>6</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -2845,10 +2849,10 @@
         <v>10</v>
       </c>
       <c r="J8" t="n">
-        <v>18.27</v>
+        <v>40</v>
       </c>
       <c r="K8" t="n">
-        <v>10.32</v>
+        <v>80</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -2862,31 +2866,31 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>INJUSDT</t>
+          <t>WLFIUSDT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Injective</t>
+          <t>World Liberty Financial</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>$3.22</t>
+          <t>$0.11</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>$321.91M</t>
+          <t>$3.00B</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>$1.46M</t>
+          <t>$13.50M</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2.97</v>
+        <v>3.83</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -2895,10 +2899,10 @@
         <v>10</v>
       </c>
       <c r="J9" t="n">
-        <v>9.73</v>
+        <v>18.27</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>10.32</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -2912,31 +2916,31 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CHZUSDT</t>
+          <t>INJUSDT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chiliz</t>
+          <t>Injective</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>$0.03</t>
+          <t>$3.18</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>$345.50M</t>
+          <t>$317.95M</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>$3.47M</t>
+          <t>$1.66M</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2.8</v>
+        <v>2.97</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -2945,7 +2949,7 @@
         <v>10</v>
       </c>
       <c r="J10" t="n">
-        <v>8</v>
+        <v>9.73</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -2962,27 +2966,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>TONUSDT</t>
+          <t>HYPEUSDT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Toncoin</t>
+          <t>Hyperliquid</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>$1.33</t>
+          <t>$26.45</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>$3.26B</t>
+          <t>$6.85B</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>$3.10M</t>
+          <t>$8.39M</t>
         </is>
       </c>
       <c r="G11" t="n">
